--- a/Project/DiceWarrior/LubanTool/Datas/物品表.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/物品表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17470"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -173,31 +173,22 @@
     <t>通用货币2</t>
   </si>
   <si>
-    <t>回退道具</t>
+    <t>道具1</t>
   </si>
   <si>
     <t>prop3</t>
   </si>
   <si>
-    <t>通用货币3</t>
-  </si>
-  <si>
-    <t>清除道具</t>
+    <t>道具2</t>
   </si>
   <si>
     <t>prop4</t>
   </si>
   <si>
-    <t>通用货币4</t>
-  </si>
-  <si>
-    <t>洗牌道具</t>
+    <t>道具3</t>
   </si>
   <si>
     <t>prop5</t>
-  </si>
-  <si>
-    <t>通用货币5</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1197,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AC27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
@@ -1495,7 +1486,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -1509,13 +1500,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
@@ -1529,13 +1520,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3">
         <v>100</v>

--- a/Project/DiceWarrior/LubanTool/Datas/物品表.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/物品表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\ProjectDiceWarrior\Project\DiceWarrior\LubanTool\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17470"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="338">
   <si>
     <t>##var</t>
   </si>
@@ -36,7 +41,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="等线"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -46,7 +51,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="等线"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -64,7 +69,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="等线"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -74,7 +79,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="等线"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -88,6 +93,9 @@
     <t>quality</t>
   </si>
   <si>
+    <t>prefabName</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -116,7 +124,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="等线"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -126,7 +134,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="等线"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -149,6 +157,9 @@
     <t>品质</t>
   </si>
   <si>
+    <t>预制体名称</t>
+  </si>
+  <si>
     <t>测试物品</t>
   </si>
   <si>
@@ -189,6 +200,909 @@
   </si>
   <si>
     <t>prop5</t>
+  </si>
+  <si>
+    <t>素白渐变素彩蛋</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Egg 01A：素白配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 01A</t>
+  </si>
+  <si>
+    <t>琥珀渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01B：琥珀配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 01B</t>
+  </si>
+  <si>
+    <t>蔷薇渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01C：蔷薇配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 01C</t>
+  </si>
+  <si>
+    <t>青碧渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01D：青碧配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 01D</t>
+  </si>
+  <si>
+    <t>靛蓝渐变素彩蛋</t>
+  </si>
+  <si>
+    <t>Egg 01E：靛蓝配色的渐变素彩蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 01E</t>
+  </si>
+  <si>
+    <t>金黄山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02A：金黄配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 02A</t>
+  </si>
+  <si>
+    <t>紫青山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02B：紫青配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 02B</t>
+  </si>
+  <si>
+    <t>绯红山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02C：绯红配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 02C</t>
+  </si>
+  <si>
+    <t>珊瑚山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02D：珊瑚配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 02D</t>
+  </si>
+  <si>
+    <t>象牙山脉纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 02E：象牙配色的山脉纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 02E</t>
+  </si>
+  <si>
+    <t>桃粉彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03A：桃粉配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 03A</t>
+  </si>
+  <si>
+    <t>晴蓝彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03B：晴蓝配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 03B</t>
+  </si>
+  <si>
+    <t>金橙彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03C：金橙配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 03C</t>
+  </si>
+  <si>
+    <t>玫红彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03D：玫红配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 03D</t>
+  </si>
+  <si>
+    <t>霓紫彩菱纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 03E：霓紫配色的彩菱纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 03E</t>
+  </si>
+  <si>
+    <t>薄荷横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04A：薄荷配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 04A</t>
+  </si>
+  <si>
+    <t>玫棕横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04B：玫棕配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 04B</t>
+  </si>
+  <si>
+    <t>海蓝横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04C：海蓝配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 04C</t>
+  </si>
+  <si>
+    <t>翠绿横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04D：翠绿配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 04D</t>
+  </si>
+  <si>
+    <t>紫罗兰横带纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 04E：紫罗兰配色的横带纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 04E</t>
+  </si>
+  <si>
+    <t>猩红熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05A：猩红配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 05A</t>
+  </si>
+  <si>
+    <t>橙紫熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05B：橙紫配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 05B</t>
+  </si>
+  <si>
+    <t>柠檬熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05C：柠檬配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 05C</t>
+  </si>
+  <si>
+    <t>青黛熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05D：青黛配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 05D</t>
+  </si>
+  <si>
+    <t>暗红熔岩滴纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 05E：暗红配色的熔岩滴纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 05E</t>
+  </si>
+  <si>
+    <t>烈焰闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06A：烈焰配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 06A</t>
+  </si>
+  <si>
+    <t>铜棕闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06B：铜棕配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 06B</t>
+  </si>
+  <si>
+    <t>荧黄闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06C：荧黄配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 06C</t>
+  </si>
+  <si>
+    <t>碧绿闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06D：碧绿配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 06D</t>
+  </si>
+  <si>
+    <t>紫晶闪电纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 06E：紫晶配色的闪电纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 06E</t>
+  </si>
+  <si>
+    <t>橙绿徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07A：橙绿配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 07A</t>
+  </si>
+  <si>
+    <t>莓果徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07B：莓果配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 07B</t>
+  </si>
+  <si>
+    <t>紫金徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07C：紫金配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 07C</t>
+  </si>
+  <si>
+    <t>明黄徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07D：明黄配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 07D</t>
+  </si>
+  <si>
+    <t>柠青徽章腰带蛋</t>
+  </si>
+  <si>
+    <t>Egg 07E：柠青配色的徽章腰带蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 07E</t>
+  </si>
+  <si>
+    <t>粉灰碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08A：粉灰配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 08A</t>
+  </si>
+  <si>
+    <t>薰衣草碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08B：薰衣草配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 08B</t>
+  </si>
+  <si>
+    <t>雾蓝碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08C：雾蓝配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 08C</t>
+  </si>
+  <si>
+    <t>深海碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08D：深海配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 08D</t>
+  </si>
+  <si>
+    <t>墨黑碎片斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 08E：墨黑配色的碎片斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 08E</t>
+  </si>
+  <si>
+    <t>金黄顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09A：金黄配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 09A</t>
+  </si>
+  <si>
+    <t>荧绿顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09B：荧绿配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 09B</t>
+  </si>
+  <si>
+    <t>青蓝顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09C：青蓝配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 09C</t>
+  </si>
+  <si>
+    <t>紫晶顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09D：紫晶配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 09D</t>
+  </si>
+  <si>
+    <t>珊瑚顶部裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 09E：珊瑚配色的顶部裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 09E</t>
+  </si>
+  <si>
+    <t>莓红宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10A：莓红配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 10A</t>
+  </si>
+  <si>
+    <t>翡翠宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10B：翡翠配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 10B</t>
+  </si>
+  <si>
+    <t>青紫宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10C：青紫配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 10C</t>
+  </si>
+  <si>
+    <t>金黄宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10D：金黄配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 10D</t>
+  </si>
+  <si>
+    <t>玫紫宝石斑点蛋</t>
+  </si>
+  <si>
+    <t>Egg 10E：玫紫配色的宝石斑点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 10E</t>
+  </si>
+  <si>
+    <t>南瓜南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11A：南瓜配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 11A</t>
+  </si>
+  <si>
+    <t>朱红南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11B：朱红配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 11B</t>
+  </si>
+  <si>
+    <t>紫莓南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11C：紫莓配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 11C</t>
+  </si>
+  <si>
+    <t>青柠南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11D：青柠配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 11D</t>
+  </si>
+  <si>
+    <t>雪白南瓜纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 11E：雪白配色的南瓜纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 11E</t>
+  </si>
+  <si>
+    <t>莓粉圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12A：莓粉配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 12A</t>
+  </si>
+  <si>
+    <t>蔚蓝圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12B：蔚蓝配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 12B</t>
+  </si>
+  <si>
+    <t>青柠圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12C：青柠配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 12C</t>
+  </si>
+  <si>
+    <t>黄绿圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12D：黄绿配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 12D</t>
+  </si>
+  <si>
+    <t>青紫圆点斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 12E：青紫配色的圆点斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 12E</t>
+  </si>
+  <si>
+    <t>翡翠菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13A：翡翠配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 13A</t>
+  </si>
+  <si>
+    <t>珊瑚菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13B：珊瑚配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 13B</t>
+  </si>
+  <si>
+    <t>紫罗兰菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13C：紫罗兰配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 13C</t>
+  </si>
+  <si>
+    <t>晴蓝菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13D：晴蓝配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 13D</t>
+  </si>
+  <si>
+    <t>莓红菱角花瓣蛋</t>
+  </si>
+  <si>
+    <t>Egg 13E：莓红配色的菱角花瓣蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 13E</t>
+  </si>
+  <si>
+    <t>紫金金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14A：紫金配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 14A</t>
+  </si>
+  <si>
+    <t>深青金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14B：深青配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 14B</t>
+  </si>
+  <si>
+    <t>玫红金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14C：玫红配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 14C</t>
+  </si>
+  <si>
+    <t>橙金金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14D：橙金配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 14D</t>
+  </si>
+  <si>
+    <t>翠绿金线星点蛋</t>
+  </si>
+  <si>
+    <t>Egg 14E：翠绿配色的金线星点蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 14E</t>
+  </si>
+  <si>
+    <t>蓝紫宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15A：蓝紫配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 15A</t>
+  </si>
+  <si>
+    <t>玫粉宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15B：玫粉配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 15B</t>
+  </si>
+  <si>
+    <t>绯红宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15C：绯红配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 15C</t>
+  </si>
+  <si>
+    <t>金蓝宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15D：金蓝配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 15D</t>
+  </si>
+  <si>
+    <t>翡翠宝石皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 15E：翡翠配色的宝石皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 15E</t>
+  </si>
+  <si>
+    <t>铜焰暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16A：铜焰配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 16A</t>
+  </si>
+  <si>
+    <t>翠焰暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16B：翠焰配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 16B</t>
+  </si>
+  <si>
+    <t>紫焰暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16C：紫焰配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 16C</t>
+  </si>
+  <si>
+    <t>幽紫暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16D：幽紫配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 16D</t>
+  </si>
+  <si>
+    <t>琥珀暗影渐变蛋</t>
+  </si>
+  <si>
+    <t>Egg 16E：琥珀配色的暗影渐变蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 16E</t>
+  </si>
+  <si>
+    <t>幽紫灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17A：幽紫配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 17A</t>
+  </si>
+  <si>
+    <t>午夜蓝灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17B：午夜蓝配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 17B</t>
+  </si>
+  <si>
+    <t>青绿灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17C：青绿配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 17C</t>
+  </si>
+  <si>
+    <t>棕橙灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17D：棕橙配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 17D</t>
+  </si>
+  <si>
+    <t>灰黑灵火斑纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 17E：灰黑配色的灵火斑纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 17E</t>
+  </si>
+  <si>
+    <t>紫黑熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18A：紫黑配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 18A</t>
+  </si>
+  <si>
+    <t>靛蓝熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18B：靛蓝配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 18B</t>
+  </si>
+  <si>
+    <t>深青熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18C：深青配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 18C</t>
+  </si>
+  <si>
+    <t>棕红熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18D：棕红配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 18D</t>
+  </si>
+  <si>
+    <t>草绿熔岩波纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 18E：草绿配色的熔岩波纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 18E</t>
+  </si>
+  <si>
+    <t>紫蓝锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19A：紫蓝配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 19A</t>
+  </si>
+  <si>
+    <t>森林绿锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19B：森林绿配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 19B</t>
+  </si>
+  <si>
+    <t>金沙锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19C：金沙配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 19C</t>
+  </si>
+  <si>
+    <t>海蓝锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19D：海蓝配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 19D</t>
+  </si>
+  <si>
+    <t>莓紫锯齿皇冠蛋</t>
+  </si>
+  <si>
+    <t>Egg 19E：莓紫配色的锯齿皇冠蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 19E</t>
+  </si>
+  <si>
+    <t>紫粉花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20A：紫粉配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 20A</t>
+  </si>
+  <si>
+    <t>靛红花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20B：靛红配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 20B</t>
+  </si>
+  <si>
+    <t>杏绿花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20C：杏绿配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 20C</t>
+  </si>
+  <si>
+    <t>香槟花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20D：香槟配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 20D</t>
+  </si>
+  <si>
+    <t>青翠花瓣裂纹蛋</t>
+  </si>
+  <si>
+    <t>Egg 20E：青翠配色的花瓣裂纹蛋，来源于100 Eggs Pack Cute Series预制体。</t>
+  </si>
+  <si>
+    <t>Egg 20E</t>
   </si>
 </sst>
 </file>
@@ -201,50 +1115,49 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -252,15 +1165,13 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -268,7 +1179,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -276,7 +1186,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -284,77 +1193,68 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,7 +1275,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,6 +1283,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
       </patternFill>
     </fill>
     <fill>
@@ -423,13 +1341,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,19 +1359,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,19 +1383,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,19 +1407,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,19 +1431,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,24 +1455,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -578,23 +1496,153 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
       </left>
       <right/>
       <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color theme="0"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color theme="0"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -628,7 +1676,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -715,52 +1763,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -769,83 +1817,83 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -859,22 +1907,103 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -929,7 +2058,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -982,73 +2325,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1060,23 +2343,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1086,23 +2369,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1110,26 +2393,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1164,17 +2444,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1196,416 +2476,2978 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="59.625" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="16.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="72.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="11.9166666666667" customWidth="1"/>
+    <col min="7" max="7" width="13.0833333333333" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" ht="15.25" spans="1:29">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:29">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="14.75" spans="1:29">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:29">
-      <c r="A3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:29">
-      <c r="A4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8" t="s">
+      <c r="A4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:29">
-      <c r="A5" s="9" t="s">
+      <c r="E4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="14.5" spans="1:29">
+      <c r="A5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="D5" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="F5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
+      <c r="G5" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="B6" s="3">
+      <c r="A6" s="25"/>
+      <c r="B6" s="21">
         <v>10000</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="C6" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="21">
         <v>100</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="G6" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" s="4" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="B7" s="4">
+      <c r="A7" s="28"/>
+      <c r="B7" s="17">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="C7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="3">
+      <c r="D7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="17">
         <v>100</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="G7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="30"/>
     </row>
     <row r="8" s="4" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="B8" s="4">
+      <c r="A8" s="25"/>
+      <c r="B8" s="21">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="C8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="3">
+      <c r="D8" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="21">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="G8" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="26"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="27"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="B9" s="4">
+      <c r="A9" s="28"/>
+      <c r="B9" s="17">
         <v>3</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="C9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="17">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="G9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="30"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="B10" s="4">
+      <c r="A10" s="25"/>
+      <c r="B10" s="21">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="C10" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="21">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="G10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="27"/>
     </row>
     <row r="11" s="4" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="B11" s="4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="17">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="C11" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="17">
         <v>100</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="26.1" customHeight="1"/>
+      <c r="G11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="29"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="30"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
+      <c r="A12" s="31"/>
+      <c r="B12" s="26">
+        <v>10001</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="21"/>
+      <c r="J12" s="27"/>
+    </row>
     <row r="13" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="29">
+        <v>10002</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="29">
+        <v>0</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="30"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="26">
+        <v>10003</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="26">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="21"/>
+      <c r="J14" s="27"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="29">
+        <v>10004</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="29">
+        <v>0</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="30"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:29">
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" s="3" customFormat="1" ht="25.5" customHeight="1" spans="3:5">
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" s="3" customFormat="1" ht="26.1" customHeight="1" spans="3:5">
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" s="3" customFormat="1" ht="26.1" customHeight="1"/>
-    <row r="27" s="3" customFormat="1" ht="26.1" customHeight="1"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="26">
+        <v>10005</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="26">
+        <v>0</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="21"/>
+      <c r="J16" s="27"/>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A17" s="32"/>
+      <c r="B17" s="29">
+        <v>10006</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="29">
+        <v>0</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="30"/>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A18" s="31"/>
+      <c r="B18" s="26">
+        <v>10007</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="26">
+        <v>0</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="21"/>
+      <c r="J18" s="27"/>
+    </row>
+    <row r="19" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A19" s="32"/>
+      <c r="B19" s="29">
+        <v>10008</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="29">
+        <v>0</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" s="3" customFormat="1" ht="25.5" customHeight="1" spans="1:10">
+      <c r="A20" s="31"/>
+      <c r="B20" s="26">
+        <v>10009</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="26">
+        <v>0</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="27"/>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A21" s="32"/>
+      <c r="B21" s="29">
+        <v>10010</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="29">
+        <v>0</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="30"/>
+    </row>
+    <row r="22" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A22" s="31"/>
+      <c r="B22" s="26">
+        <v>10011</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="26">
+        <v>0</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" s="21"/>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A23" s="32"/>
+      <c r="B23" s="29">
+        <v>10012</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="29">
+        <v>0</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="17"/>
+      <c r="J23" s="30"/>
+    </row>
+    <row r="24" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A24" s="31"/>
+      <c r="B24" s="26">
+        <v>10013</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="26">
+        <v>0</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="21"/>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A25" s="32"/>
+      <c r="B25" s="29">
+        <v>10014</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="29">
+        <v>0</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="I25" s="17"/>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A26" s="31"/>
+      <c r="B26" s="26">
+        <v>10015</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" s="21"/>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
+      <c r="A27" s="32"/>
+      <c r="B27" s="29">
+        <v>10016</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="29">
+        <v>0</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="17"/>
+      <c r="J27" s="30"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="31"/>
+      <c r="B28" s="26">
+        <v>10017</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="26">
+        <v>0</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="26"/>
+      <c r="J28" s="33"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="32"/>
+      <c r="B29" s="29">
+        <v>10018</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="29"/>
+      <c r="J29" s="34"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="31"/>
+      <c r="B30" s="26">
+        <v>10019</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="26">
+        <v>0</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="I30" s="26"/>
+      <c r="J30" s="33"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="32"/>
+      <c r="B31" s="29">
+        <v>10020</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="29">
+        <v>0</v>
+      </c>
+      <c r="G31" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="29"/>
+      <c r="J31" s="34"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="31"/>
+      <c r="B32" s="26">
+        <v>10021</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="26">
+        <v>0</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" s="26"/>
+      <c r="J32" s="33"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="32"/>
+      <c r="B33" s="29">
+        <v>10022</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="29">
+        <v>0</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" s="29"/>
+      <c r="J33" s="34"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="31"/>
+      <c r="B34" s="26">
+        <v>10023</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="26">
+        <v>0</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="26"/>
+      <c r="J34" s="33"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="32"/>
+      <c r="B35" s="29">
+        <v>10024</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="29">
+        <v>0</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="I35" s="29"/>
+      <c r="J35" s="34"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="31"/>
+      <c r="B36" s="26">
+        <v>10025</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="26">
+        <v>0</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="33"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="32"/>
+      <c r="B37" s="29">
+        <v>10026</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" s="29">
+        <v>0</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="I37" s="29"/>
+      <c r="J37" s="34"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="31"/>
+      <c r="B38" s="26">
+        <v>10027</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" s="26">
+        <v>0</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I38" s="26"/>
+      <c r="J38" s="33"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="32"/>
+      <c r="B39" s="29">
+        <v>10028</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F39" s="29">
+        <v>0</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="I39" s="29"/>
+      <c r="J39" s="34"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="31"/>
+      <c r="B40" s="26">
+        <v>10029</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" s="26">
+        <v>0</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I40" s="26"/>
+      <c r="J40" s="33"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="32"/>
+      <c r="B41" s="29">
+        <v>10030</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="29">
+        <v>0</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="I41" s="29"/>
+      <c r="J41" s="34"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="31"/>
+      <c r="B42" s="26">
+        <v>10031</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F42" s="26">
+        <v>0</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="I42" s="26"/>
+      <c r="J42" s="33"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="32"/>
+      <c r="B43" s="29">
+        <v>10032</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="F43" s="29">
+        <v>0</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="29"/>
+      <c r="J43" s="34"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="31"/>
+      <c r="B44" s="26">
+        <v>10033</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F44" s="26">
+        <v>0</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" s="26"/>
+      <c r="J44" s="33"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="32"/>
+      <c r="B45" s="29">
+        <v>10034</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" s="29">
+        <v>0</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="I45" s="29"/>
+      <c r="J45" s="34"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="31"/>
+      <c r="B46" s="26">
+        <v>10035</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F46" s="26">
+        <v>0</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I46" s="26"/>
+      <c r="J46" s="33"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="32"/>
+      <c r="B47" s="29">
+        <v>10036</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="29">
+        <v>0</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="I47" s="29"/>
+      <c r="J47" s="34"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="31"/>
+      <c r="B48" s="26">
+        <v>10037</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F48" s="26">
+        <v>0</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="I48" s="26"/>
+      <c r="J48" s="33"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="32"/>
+      <c r="B49" s="29">
+        <v>10038</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="29">
+        <v>0</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="I49" s="29"/>
+      <c r="J49" s="34"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="31"/>
+      <c r="B50" s="26">
+        <v>10039</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F50" s="26">
+        <v>0</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="I50" s="26"/>
+      <c r="J50" s="33"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="32"/>
+      <c r="B51" s="29">
+        <v>10040</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F51" s="29">
+        <v>0</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="I51" s="29"/>
+      <c r="J51" s="34"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="31"/>
+      <c r="B52" s="26">
+        <v>10041</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F52" s="26">
+        <v>0</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="I52" s="26"/>
+      <c r="J52" s="33"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="32"/>
+      <c r="B53" s="29">
+        <v>10042</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" s="29">
+        <v>0</v>
+      </c>
+      <c r="G53" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="I53" s="29"/>
+      <c r="J53" s="34"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="31"/>
+      <c r="B54" s="26">
+        <v>10043</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F54" s="26">
+        <v>0</v>
+      </c>
+      <c r="G54" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="I54" s="26"/>
+      <c r="J54" s="33"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="32"/>
+      <c r="B55" s="29">
+        <v>10044</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55" s="29">
+        <v>0</v>
+      </c>
+      <c r="G55" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I55" s="29"/>
+      <c r="J55" s="34"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="31"/>
+      <c r="B56" s="26">
+        <v>10045</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56" s="26">
+        <v>0</v>
+      </c>
+      <c r="G56" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I56" s="26"/>
+      <c r="J56" s="33"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="32"/>
+      <c r="B57" s="29">
+        <v>10046</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F57" s="29">
+        <v>0</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="I57" s="29"/>
+      <c r="J57" s="34"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="31"/>
+      <c r="B58" s="26">
+        <v>10047</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="26">
+        <v>0</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="I58" s="26"/>
+      <c r="J58" s="33"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="32"/>
+      <c r="B59" s="29">
+        <v>10048</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="F59" s="29">
+        <v>0</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="I59" s="29"/>
+      <c r="J59" s="34"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="31"/>
+      <c r="B60" s="26">
+        <v>10049</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="F60" s="26">
+        <v>0</v>
+      </c>
+      <c r="G60" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="I60" s="26"/>
+      <c r="J60" s="33"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="32"/>
+      <c r="B61" s="29">
+        <v>10050</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="F61" s="29">
+        <v>0</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="I61" s="29"/>
+      <c r="J61" s="34"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="31"/>
+      <c r="B62" s="26">
+        <v>10051</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="F62" s="26">
+        <v>0</v>
+      </c>
+      <c r="G62" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="I62" s="26"/>
+      <c r="J62" s="33"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="32"/>
+      <c r="B63" s="29">
+        <v>10052</v>
+      </c>
+      <c r="C63" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F63" s="29">
+        <v>0</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I63" s="29"/>
+      <c r="J63" s="34"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="31"/>
+      <c r="B64" s="26">
+        <v>10053</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F64" s="26">
+        <v>0</v>
+      </c>
+      <c r="G64" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="I64" s="26"/>
+      <c r="J64" s="33"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="32"/>
+      <c r="B65" s="29">
+        <v>10054</v>
+      </c>
+      <c r="C65" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E65" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="F65" s="29">
+        <v>0</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="I65" s="29"/>
+      <c r="J65" s="34"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="31"/>
+      <c r="B66" s="26">
+        <v>10055</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F66" s="26">
+        <v>0</v>
+      </c>
+      <c r="G66" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="I66" s="26"/>
+      <c r="J66" s="33"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="32"/>
+      <c r="B67" s="29">
+        <v>10056</v>
+      </c>
+      <c r="C67" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E67" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="F67" s="29">
+        <v>0</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="I67" s="29"/>
+      <c r="J67" s="34"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="31"/>
+      <c r="B68" s="26">
+        <v>10057</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F68" s="26">
+        <v>0</v>
+      </c>
+      <c r="G68" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="I68" s="26"/>
+      <c r="J68" s="33"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="32"/>
+      <c r="B69" s="29">
+        <v>10058</v>
+      </c>
+      <c r="C69" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="F69" s="29">
+        <v>0</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="I69" s="29"/>
+      <c r="J69" s="34"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="31"/>
+      <c r="B70" s="26">
+        <v>10059</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="D70" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="F70" s="26">
+        <v>0</v>
+      </c>
+      <c r="G70" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="I70" s="26"/>
+      <c r="J70" s="33"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="32"/>
+      <c r="B71" s="29">
+        <v>10060</v>
+      </c>
+      <c r="C71" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="F71" s="29">
+        <v>0</v>
+      </c>
+      <c r="G71" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="I71" s="29"/>
+      <c r="J71" s="34"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="31"/>
+      <c r="B72" s="26">
+        <v>10061</v>
+      </c>
+      <c r="C72" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="F72" s="26">
+        <v>0</v>
+      </c>
+      <c r="G72" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="I72" s="26"/>
+      <c r="J72" s="33"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="32"/>
+      <c r="B73" s="29">
+        <v>10062</v>
+      </c>
+      <c r="C73" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E73" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="F73" s="29">
+        <v>0</v>
+      </c>
+      <c r="G73" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="I73" s="29"/>
+      <c r="J73" s="34"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="31"/>
+      <c r="B74" s="26">
+        <v>10063</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D74" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="F74" s="26">
+        <v>0</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="I74" s="26"/>
+      <c r="J74" s="33"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="32"/>
+      <c r="B75" s="29">
+        <v>10064</v>
+      </c>
+      <c r="C75" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="F75" s="29">
+        <v>0</v>
+      </c>
+      <c r="G75" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="I75" s="29"/>
+      <c r="J75" s="34"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="31"/>
+      <c r="B76" s="26">
+        <v>10065</v>
+      </c>
+      <c r="C76" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="D76" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F76" s="26">
+        <v>0</v>
+      </c>
+      <c r="G76" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="I76" s="26"/>
+      <c r="J76" s="33"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="32"/>
+      <c r="B77" s="29">
+        <v>10066</v>
+      </c>
+      <c r="C77" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="F77" s="29">
+        <v>0</v>
+      </c>
+      <c r="G77" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H77" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="I77" s="29"/>
+      <c r="J77" s="34"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="31"/>
+      <c r="B78" s="26">
+        <v>10067</v>
+      </c>
+      <c r="C78" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D78" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="F78" s="26">
+        <v>0</v>
+      </c>
+      <c r="G78" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="I78" s="26"/>
+      <c r="J78" s="33"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="32"/>
+      <c r="B79" s="29">
+        <v>10068</v>
+      </c>
+      <c r="C79" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="F79" s="29">
+        <v>0</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H79" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="I79" s="29"/>
+      <c r="J79" s="34"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="31"/>
+      <c r="B80" s="26">
+        <v>10069</v>
+      </c>
+      <c r="C80" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F80" s="26">
+        <v>0</v>
+      </c>
+      <c r="G80" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="I80" s="26"/>
+      <c r="J80" s="33"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="32"/>
+      <c r="B81" s="29">
+        <v>10070</v>
+      </c>
+      <c r="C81" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="F81" s="29">
+        <v>0</v>
+      </c>
+      <c r="G81" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="I81" s="29"/>
+      <c r="J81" s="34"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="31"/>
+      <c r="B82" s="26">
+        <v>10071</v>
+      </c>
+      <c r="C82" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="F82" s="26">
+        <v>0</v>
+      </c>
+      <c r="G82" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="I82" s="26"/>
+      <c r="J82" s="33"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="32"/>
+      <c r="B83" s="29">
+        <v>10072</v>
+      </c>
+      <c r="C83" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="F83" s="29">
+        <v>0</v>
+      </c>
+      <c r="G83" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="I83" s="29"/>
+      <c r="J83" s="34"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="31"/>
+      <c r="B84" s="26">
+        <v>10073</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="F84" s="26">
+        <v>0</v>
+      </c>
+      <c r="G84" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="I84" s="26"/>
+      <c r="J84" s="33"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="32"/>
+      <c r="B85" s="29">
+        <v>10074</v>
+      </c>
+      <c r="C85" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="F85" s="29">
+        <v>0</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="I85" s="29"/>
+      <c r="J85" s="34"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="31"/>
+      <c r="B86" s="26">
+        <v>10075</v>
+      </c>
+      <c r="C86" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F86" s="26">
+        <v>0</v>
+      </c>
+      <c r="G86" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="I86" s="26"/>
+      <c r="J86" s="33"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="32"/>
+      <c r="B87" s="29">
+        <v>10076</v>
+      </c>
+      <c r="C87" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="D87" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="F87" s="29">
+        <v>0</v>
+      </c>
+      <c r="G87" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="I87" s="29"/>
+      <c r="J87" s="34"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="31"/>
+      <c r="B88" s="26">
+        <v>10077</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D88" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F88" s="26">
+        <v>0</v>
+      </c>
+      <c r="G88" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="I88" s="26"/>
+      <c r="J88" s="33"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="32"/>
+      <c r="B89" s="29">
+        <v>10078</v>
+      </c>
+      <c r="C89" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="D89" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F89" s="29">
+        <v>0</v>
+      </c>
+      <c r="G89" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="I89" s="29"/>
+      <c r="J89" s="34"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="31"/>
+      <c r="B90" s="26">
+        <v>10079</v>
+      </c>
+      <c r="C90" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="D90" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="F90" s="26">
+        <v>0</v>
+      </c>
+      <c r="G90" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="I90" s="26"/>
+      <c r="J90" s="33"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="32"/>
+      <c r="B91" s="29">
+        <v>10080</v>
+      </c>
+      <c r="C91" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="D91" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="F91" s="29">
+        <v>0</v>
+      </c>
+      <c r="G91" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="I91" s="29"/>
+      <c r="J91" s="34"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="31"/>
+      <c r="B92" s="26">
+        <v>10081</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="D92" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="F92" s="26">
+        <v>0</v>
+      </c>
+      <c r="G92" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="I92" s="26"/>
+      <c r="J92" s="33"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="32"/>
+      <c r="B93" s="29">
+        <v>10082</v>
+      </c>
+      <c r="C93" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="D93" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="F93" s="29">
+        <v>0</v>
+      </c>
+      <c r="G93" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="I93" s="29"/>
+      <c r="J93" s="34"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="31"/>
+      <c r="B94" s="26">
+        <v>10083</v>
+      </c>
+      <c r="C94" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="F94" s="26">
+        <v>0</v>
+      </c>
+      <c r="G94" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="I94" s="26"/>
+      <c r="J94" s="33"/>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="32"/>
+      <c r="B95" s="29">
+        <v>10084</v>
+      </c>
+      <c r="C95" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F95" s="29">
+        <v>0</v>
+      </c>
+      <c r="G95" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="I95" s="29"/>
+      <c r="J95" s="34"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="31"/>
+      <c r="B96" s="26">
+        <v>10085</v>
+      </c>
+      <c r="C96" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="D96" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="F96" s="26">
+        <v>0</v>
+      </c>
+      <c r="G96" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="I96" s="26"/>
+      <c r="J96" s="33"/>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="32"/>
+      <c r="B97" s="29">
+        <v>10086</v>
+      </c>
+      <c r="C97" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="D97" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="F97" s="29">
+        <v>0</v>
+      </c>
+      <c r="G97" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="I97" s="29"/>
+      <c r="J97" s="34"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="31"/>
+      <c r="B98" s="26">
+        <v>10087</v>
+      </c>
+      <c r="C98" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="D98" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="F98" s="26">
+        <v>0</v>
+      </c>
+      <c r="G98" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="I98" s="26"/>
+      <c r="J98" s="33"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="32"/>
+      <c r="B99" s="29">
+        <v>10088</v>
+      </c>
+      <c r="C99" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E99" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="F99" s="29">
+        <v>0</v>
+      </c>
+      <c r="G99" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="I99" s="29"/>
+      <c r="J99" s="34"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="31"/>
+      <c r="B100" s="26">
+        <v>10089</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="D100" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="F100" s="26">
+        <v>0</v>
+      </c>
+      <c r="G100" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H100" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="I100" s="26"/>
+      <c r="J100" s="33"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="32"/>
+      <c r="B101" s="29">
+        <v>10090</v>
+      </c>
+      <c r="C101" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="D101" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E101" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="F101" s="29">
+        <v>0</v>
+      </c>
+      <c r="G101" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="I101" s="29"/>
+      <c r="J101" s="34"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="31"/>
+      <c r="B102" s="26">
+        <v>10091</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="D102" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="F102" s="26">
+        <v>0</v>
+      </c>
+      <c r="G102" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="I102" s="26"/>
+      <c r="J102" s="33"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="32"/>
+      <c r="B103" s="29">
+        <v>10092</v>
+      </c>
+      <c r="C103" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="D103" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="F103" s="29">
+        <v>0</v>
+      </c>
+      <c r="G103" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="I103" s="29"/>
+      <c r="J103" s="34"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="31"/>
+      <c r="B104" s="26">
+        <v>10093</v>
+      </c>
+      <c r="C104" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="D104" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E104" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="F104" s="26">
+        <v>0</v>
+      </c>
+      <c r="G104" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H104" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="I104" s="26"/>
+      <c r="J104" s="33"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="32"/>
+      <c r="B105" s="29">
+        <v>10094</v>
+      </c>
+      <c r="C105" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="D105" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="F105" s="29">
+        <v>0</v>
+      </c>
+      <c r="G105" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="I105" s="29"/>
+      <c r="J105" s="34"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="31"/>
+      <c r="B106" s="26">
+        <v>10095</v>
+      </c>
+      <c r="C106" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="D106" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E106" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="F106" s="26">
+        <v>0</v>
+      </c>
+      <c r="G106" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="I106" s="26"/>
+      <c r="J106" s="33"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="32"/>
+      <c r="B107" s="29">
+        <v>10096</v>
+      </c>
+      <c r="C107" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="D107" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E107" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="F107" s="29">
+        <v>0</v>
+      </c>
+      <c r="G107" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="I107" s="29"/>
+      <c r="J107" s="34"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="31"/>
+      <c r="B108" s="26">
+        <v>10097</v>
+      </c>
+      <c r="C108" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="D108" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F108" s="26">
+        <v>0</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H108" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="I108" s="26"/>
+      <c r="J108" s="33"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="32"/>
+      <c r="B109" s="29">
+        <v>10098</v>
+      </c>
+      <c r="C109" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="D109" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="F109" s="29">
+        <v>0</v>
+      </c>
+      <c r="G109" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="I109" s="29"/>
+      <c r="J109" s="34"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="31"/>
+      <c r="B110" s="26">
+        <v>10099</v>
+      </c>
+      <c r="C110" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="D110" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E110" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="F110" s="26">
+        <v>0</v>
+      </c>
+      <c r="G110" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="I110" s="26"/>
+      <c r="J110" s="33"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="35"/>
+      <c r="B111" s="36">
+        <v>10100</v>
+      </c>
+      <c r="C111" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="D111" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E111" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="F111" s="36">
+        <v>0</v>
+      </c>
+      <c r="G111" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="I111" s="36"/>
+      <c r="J111" s="37"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>